--- a/idecba/comex_zon.xlsx
+++ b/idecba/comex_zon.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.32.3.50\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO EXTERIOR\EXPORTACIONES\SERIES HISTORICAS EXPORTACIONES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SRV03\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO EXTERIOR\EXPORTACIONES\SERIES HISTORICAS EXPORTACIONES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87324F01-1836-4C31-8F1A-0CEB96145014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10830"/>
   </bookViews>
   <sheets>
     <sheet name="AX_CX_ZON" sheetId="1" r:id="rId1"/>
@@ -174,9 +173,6 @@
     <t>USMCA</t>
   </si>
   <si>
-    <t>2023*</t>
-  </si>
-  <si>
     <t>Desde 2020 el tratado USMCA reemplazó al NAFTA.</t>
   </si>
   <si>
@@ -231,17 +227,20 @@
     <t>2025*</t>
   </si>
   <si>
-    <t xml:space="preserve">Exportaciones (millones de dólares) por continente y zona económica. Ciudad de Buenos Aires. Años 2000/2025 </t>
-  </si>
-  <si>
     <t>Monto de las exportaciones de bienes de la Ciudad de Buenos Aires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exportaciones (millones de dólares) por continente y zona económica. Ciudad de Buenos Aires. Años 2000/1er. semestre de 2026 </t>
+  </si>
+  <si>
+    <t>1er. sem. 2026*</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="25">
     <numFmt numFmtId="5" formatCode="&quot;$&quot;\ #,##0;\-&quot;$&quot;\ #,##0"/>
     <numFmt numFmtId="7" formatCode="&quot;$&quot;\ #,##0.00;\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -266,6 +265,7 @@
     <numFmt numFmtId="182" formatCode="_(&quot;N$&quot;* #,##0_);_(&quot;N$&quot;* \(#,##0\);_(&quot;N$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="183" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="184" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="185" formatCode="0.0%"/>
   </numFmts>
   <fonts count="44" x14ac:knownFonts="1">
     <font>
@@ -986,7 +986,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="120">
+  <cellStyleXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1203,8 +1203,9 @@
     </xf>
     <xf numFmtId="3" fontId="39" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1313,6 +1314,7 @@
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="120" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1326,127 +1328,128 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="120">
-    <cellStyle name="20% - Énfasis1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="20% - Énfasis2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="20% - Énfasis3 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="20% - Énfasis4 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="20% - Énfasis5 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="20% - Énfasis6 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="40% - Énfasis1 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="40% - Énfasis2 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="40% - Énfasis3 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="40% - Énfasis4 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="40% - Énfasis5 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="40% - Énfasis6 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="60% - Énfasis1 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="60% - Énfasis2 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="60% - Énfasis3 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="60% - Énfasis4 2" xfId="16" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="60% - Énfasis5 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="60% - Énfasis6 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="ANCLAS,REZONES Y SUS PARTES,DE FUNDICION,DE HIERRO O DE ACERO" xfId="90" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="ANCLAS,REZONES Y SUS PARTES,DE FUNDICION,DE HIERRO O DE ACERO 2" xfId="91" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="Buena 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="Cabecera 1" xfId="92" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="Cabecera 2" xfId="93" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="Cabezal" xfId="53" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="Cabezal 2" xfId="94" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
-    <cellStyle name="Cálculo 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="Celda de comprobación 2" xfId="21" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
-    <cellStyle name="Celda vinculada 2" xfId="22" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
-    <cellStyle name="coltit" xfId="54" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
-    <cellStyle name="Columna títulos" xfId="55" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
-    <cellStyle name="Comma" xfId="56" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
-    <cellStyle name="Comma 2" xfId="95" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
-    <cellStyle name="Comma0" xfId="57" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
-    <cellStyle name="Comma0 2" xfId="96" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
-    <cellStyle name="cuadro" xfId="58" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
-    <cellStyle name="Currency" xfId="59" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
-    <cellStyle name="Currency 2" xfId="97" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
-    <cellStyle name="Currency0" xfId="60" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
-    <cellStyle name="Currency0 2" xfId="98" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
-    <cellStyle name="Date" xfId="61" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
-    <cellStyle name="Date 2" xfId="99" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
-    <cellStyle name="datos" xfId="62" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
-    <cellStyle name="Encabezado" xfId="63" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
-    <cellStyle name="Encabezado 4 2" xfId="23" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
-    <cellStyle name="Énfasis1 2" xfId="24" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
-    <cellStyle name="Énfasis2 2" xfId="25" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
-    <cellStyle name="Énfasis3 2" xfId="26" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
-    <cellStyle name="Énfasis4 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
-    <cellStyle name="Énfasis5 2" xfId="28" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
-    <cellStyle name="Énfasis6 2" xfId="29" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="Entrada 2" xfId="30" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="Estilo 1" xfId="64" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="Euro" xfId="31" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="Euro 2" xfId="65" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="F2" xfId="66" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="F2 2" xfId="100" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="F3" xfId="67" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="F3 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="F4" xfId="68" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="F4 2" xfId="102" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="F5" xfId="69" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="F5 2" xfId="103" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="F6" xfId="70" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="F6 2" xfId="104" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="F7" xfId="71" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="F7 2" xfId="105" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="F8" xfId="72" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="F8 2" xfId="106" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="Fecha" xfId="107" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="Fijo" xfId="108" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="Fin del cuadro" xfId="73" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="fincuadro" xfId="74" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="fincuadro 2" xfId="109" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="Fixed" xfId="75" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="Fixed 2" xfId="110" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="fuente" xfId="76" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="Heading 1" xfId="77" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="Heading 1 2" xfId="111" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="Heading 2" xfId="78" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="Heading 2 2" xfId="112" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="Heading1" xfId="113" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="Heading2" xfId="114" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="Incorrecto 2" xfId="32" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
+  <cellStyles count="121">
+    <cellStyle name="20% - Énfasis1 2" xfId="1"/>
+    <cellStyle name="20% - Énfasis2 2" xfId="2"/>
+    <cellStyle name="20% - Énfasis3 2" xfId="3"/>
+    <cellStyle name="20% - Énfasis4 2" xfId="4"/>
+    <cellStyle name="20% - Énfasis5 2" xfId="5"/>
+    <cellStyle name="20% - Énfasis6 2" xfId="6"/>
+    <cellStyle name="40% - Énfasis1 2" xfId="7"/>
+    <cellStyle name="40% - Énfasis2 2" xfId="8"/>
+    <cellStyle name="40% - Énfasis3 2" xfId="9"/>
+    <cellStyle name="40% - Énfasis4 2" xfId="10"/>
+    <cellStyle name="40% - Énfasis5 2" xfId="11"/>
+    <cellStyle name="40% - Énfasis6 2" xfId="12"/>
+    <cellStyle name="60% - Énfasis1 2" xfId="13"/>
+    <cellStyle name="60% - Énfasis2 2" xfId="14"/>
+    <cellStyle name="60% - Énfasis3 2" xfId="15"/>
+    <cellStyle name="60% - Énfasis4 2" xfId="16"/>
+    <cellStyle name="60% - Énfasis5 2" xfId="17"/>
+    <cellStyle name="60% - Énfasis6 2" xfId="18"/>
+    <cellStyle name="ANCLAS,REZONES Y SUS PARTES,DE FUNDICION,DE HIERRO O DE ACERO" xfId="90"/>
+    <cellStyle name="ANCLAS,REZONES Y SUS PARTES,DE FUNDICION,DE HIERRO O DE ACERO 2" xfId="91"/>
+    <cellStyle name="Buena 2" xfId="19"/>
+    <cellStyle name="Cabecera 1" xfId="92"/>
+    <cellStyle name="Cabecera 2" xfId="93"/>
+    <cellStyle name="Cabezal" xfId="53"/>
+    <cellStyle name="Cabezal 2" xfId="94"/>
+    <cellStyle name="Cálculo 2" xfId="20"/>
+    <cellStyle name="Celda de comprobación 2" xfId="21"/>
+    <cellStyle name="Celda vinculada 2" xfId="22"/>
+    <cellStyle name="coltit" xfId="54"/>
+    <cellStyle name="Columna títulos" xfId="55"/>
+    <cellStyle name="Comma" xfId="56"/>
+    <cellStyle name="Comma 2" xfId="95"/>
+    <cellStyle name="Comma0" xfId="57"/>
+    <cellStyle name="Comma0 2" xfId="96"/>
+    <cellStyle name="cuadro" xfId="58"/>
+    <cellStyle name="Currency" xfId="59"/>
+    <cellStyle name="Currency 2" xfId="97"/>
+    <cellStyle name="Currency0" xfId="60"/>
+    <cellStyle name="Currency0 2" xfId="98"/>
+    <cellStyle name="Date" xfId="61"/>
+    <cellStyle name="Date 2" xfId="99"/>
+    <cellStyle name="datos" xfId="62"/>
+    <cellStyle name="Encabezado" xfId="63"/>
+    <cellStyle name="Encabezado 4 2" xfId="23"/>
+    <cellStyle name="Énfasis1 2" xfId="24"/>
+    <cellStyle name="Énfasis2 2" xfId="25"/>
+    <cellStyle name="Énfasis3 2" xfId="26"/>
+    <cellStyle name="Énfasis4 2" xfId="27"/>
+    <cellStyle name="Énfasis5 2" xfId="28"/>
+    <cellStyle name="Énfasis6 2" xfId="29"/>
+    <cellStyle name="Entrada 2" xfId="30"/>
+    <cellStyle name="Estilo 1" xfId="64"/>
+    <cellStyle name="Euro" xfId="31"/>
+    <cellStyle name="Euro 2" xfId="65"/>
+    <cellStyle name="F2" xfId="66"/>
+    <cellStyle name="F2 2" xfId="100"/>
+    <cellStyle name="F3" xfId="67"/>
+    <cellStyle name="F3 2" xfId="101"/>
+    <cellStyle name="F4" xfId="68"/>
+    <cellStyle name="F4 2" xfId="102"/>
+    <cellStyle name="F5" xfId="69"/>
+    <cellStyle name="F5 2" xfId="103"/>
+    <cellStyle name="F6" xfId="70"/>
+    <cellStyle name="F6 2" xfId="104"/>
+    <cellStyle name="F7" xfId="71"/>
+    <cellStyle name="F7 2" xfId="105"/>
+    <cellStyle name="F8" xfId="72"/>
+    <cellStyle name="F8 2" xfId="106"/>
+    <cellStyle name="Fecha" xfId="107"/>
+    <cellStyle name="Fijo" xfId="108"/>
+    <cellStyle name="Fin del cuadro" xfId="73"/>
+    <cellStyle name="fincuadro" xfId="74"/>
+    <cellStyle name="fincuadro 2" xfId="109"/>
+    <cellStyle name="Fixed" xfId="75"/>
+    <cellStyle name="Fixed 2" xfId="110"/>
+    <cellStyle name="fuente" xfId="76"/>
+    <cellStyle name="Heading 1" xfId="77"/>
+    <cellStyle name="Heading 1 2" xfId="111"/>
+    <cellStyle name="Heading 2" xfId="78"/>
+    <cellStyle name="Heading 2 2" xfId="112"/>
+    <cellStyle name="Heading1" xfId="113"/>
+    <cellStyle name="Heading2" xfId="114"/>
+    <cellStyle name="Incorrecto 2" xfId="32"/>
     <cellStyle name="Millares" xfId="119" builtinId="3"/>
-    <cellStyle name="Millares 2" xfId="80" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
-    <cellStyle name="Millares 3" xfId="81" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="Millares 4" xfId="79" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="Millares 5" xfId="89" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="mio" xfId="33" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
-    <cellStyle name="Monetario" xfId="115" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="Monetario0" xfId="116" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="Neutral 2" xfId="34" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="Millares 2" xfId="80"/>
+    <cellStyle name="Millares 3" xfId="81"/>
+    <cellStyle name="Millares 4" xfId="79"/>
+    <cellStyle name="Millares 5" xfId="89"/>
+    <cellStyle name="mio" xfId="33"/>
+    <cellStyle name="Monetario" xfId="115"/>
+    <cellStyle name="Monetario0" xfId="116"/>
+    <cellStyle name="Neutral 2" xfId="34"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="35" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="Normal 2 2" xfId="36" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="Normal 2 3" xfId="82" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="Normal 3" xfId="37" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="Normal 3 2" xfId="83" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
-    <cellStyle name="Normal 4" xfId="52" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
-    <cellStyle name="Normal_Hoja1" xfId="38" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
-    <cellStyle name="Notas 2" xfId="39" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="Pato" xfId="40" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
-    <cellStyle name="Percent" xfId="84" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
-    <cellStyle name="Percent 2" xfId="117" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="Porcentaje 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="Porcentaje 3" xfId="42" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
-    <cellStyle name="Porcentual 2" xfId="85" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
-    <cellStyle name="Punto0" xfId="118" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
-    <cellStyle name="Salida 2" xfId="43" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
-    <cellStyle name="TableStyleLight1" xfId="44" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
-    <cellStyle name="Texto de advertencia 2" xfId="45" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
-    <cellStyle name="Texto explicativo 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
-    <cellStyle name="titulo" xfId="86" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
-    <cellStyle name="Título 1 2" xfId="47" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
-    <cellStyle name="Título 2 2" xfId="48" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
-    <cellStyle name="Título 3 2" xfId="49" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
-    <cellStyle name="Título 4" xfId="50" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
-    <cellStyle name="Total 2" xfId="51" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
-    <cellStyle name="total 3" xfId="87" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
-    <cellStyle name="totcuadro" xfId="88" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
+    <cellStyle name="Normal 2" xfId="35"/>
+    <cellStyle name="Normal 2 2" xfId="36"/>
+    <cellStyle name="Normal 2 3" xfId="82"/>
+    <cellStyle name="Normal 3" xfId="37"/>
+    <cellStyle name="Normal 3 2" xfId="83"/>
+    <cellStyle name="Normal 4" xfId="52"/>
+    <cellStyle name="Normal_Hoja1" xfId="38"/>
+    <cellStyle name="Notas 2" xfId="39"/>
+    <cellStyle name="Pato" xfId="40"/>
+    <cellStyle name="Percent" xfId="84"/>
+    <cellStyle name="Percent 2" xfId="117"/>
+    <cellStyle name="Porcentaje" xfId="120" builtinId="5"/>
+    <cellStyle name="Porcentaje 2" xfId="41"/>
+    <cellStyle name="Porcentaje 3" xfId="42"/>
+    <cellStyle name="Porcentual 2" xfId="85"/>
+    <cellStyle name="Punto0" xfId="118"/>
+    <cellStyle name="Salida 2" xfId="43"/>
+    <cellStyle name="TableStyleLight1" xfId="44"/>
+    <cellStyle name="Texto de advertencia 2" xfId="45"/>
+    <cellStyle name="Texto explicativo 2" xfId="46"/>
+    <cellStyle name="titulo" xfId="86"/>
+    <cellStyle name="Título 1 2" xfId="47"/>
+    <cellStyle name="Título 2 2" xfId="48"/>
+    <cellStyle name="Título 3 2" xfId="49"/>
+    <cellStyle name="Título 4" xfId="50"/>
+    <cellStyle name="Total 2" xfId="51"/>
+    <cellStyle name="total 3" xfId="87"/>
+    <cellStyle name="totcuadro" xfId="88"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1462,9 +1465,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1502,9 +1505,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1539,7 +1542,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1574,7 +1577,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1747,43 +1750,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AC31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" style="24" customWidth="1"/>
-    <col min="2" max="11" width="8.33203125" style="24" customWidth="1"/>
-    <col min="12" max="18" width="8.33203125" style="25" customWidth="1"/>
-    <col min="19" max="23" width="8.33203125" style="24" customWidth="1"/>
-    <col min="24" max="27" width="8.6640625" style="24" customWidth="1"/>
-    <col min="28" max="29" width="8" customWidth="1"/>
-    <col min="30" max="16384" width="11.44140625" style="24"/>
+    <col min="1" max="1" width="17.5703125" style="24" customWidth="1"/>
+    <col min="2" max="11" width="8.28515625" style="24" customWidth="1"/>
+    <col min="12" max="18" width="8.28515625" style="25" customWidth="1"/>
+    <col min="19" max="23" width="8.28515625" style="24" customWidth="1"/>
+    <col min="24" max="27" width="8.7109375" style="24" customWidth="1"/>
+    <col min="28" max="28" width="8.7109375" customWidth="1"/>
+    <col min="29" max="29" width="12.85546875" customWidth="1"/>
+    <col min="30" max="16384" width="11.42578125" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-    </row>
-    <row r="2" spans="1:27" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="AB1" s="24"/>
+    </row>
+    <row r="2" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1856,17 +1861,20 @@
       <c r="X2" s="1">
         <v>2022</v>
       </c>
-      <c r="Y2" s="1" t="s">
-        <v>44</v>
+      <c r="Y2" s="1">
+        <v>2023</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
@@ -1940,7 +1948,7 @@
         <v>311.79019289999997</v>
       </c>
       <c r="Y3" s="3">
-        <v>316.58010414000006</v>
+        <v>316.58010394000001</v>
       </c>
       <c r="Z3" s="3">
         <v>363.70608599999986</v>
@@ -1948,8 +1956,12 @@
       <c r="AA3" s="3">
         <v>409.24717071999999</v>
       </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB3" s="3">
+        <v>192.23067983000001</v>
+      </c>
+      <c r="AC3" s="44"/>
+    </row>
+    <row r="4" spans="1:29" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="27" t="s">
         <v>1</v>
       </c>
@@ -2031,8 +2043,12 @@
       <c r="AA4" s="28">
         <v>146.32976074000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB4" s="28">
+        <v>74.611859930000008</v>
+      </c>
+      <c r="AC4" s="28"/>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -2114,8 +2130,12 @@
       <c r="AA5" s="4">
         <v>99.887150019999993</v>
       </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB5" s="4">
+        <v>47.439342880000005</v>
+      </c>
+      <c r="AC5" s="44"/>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>43</v>
       </c>
@@ -2197,8 +2217,12 @@
       <c r="AA6" s="4">
         <v>12.203812699999999</v>
       </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB6" s="4">
+        <v>6.8555832699999995</v>
+      </c>
+      <c r="AC6" s="44"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -2280,8 +2304,12 @@
       <c r="AA7" s="4">
         <v>1.3084330100000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB7" s="4">
+        <v>0.59669923999999996</v>
+      </c>
+      <c r="AC7" s="44"/>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -2363,8 +2391,12 @@
       <c r="AA8" s="4">
         <v>32.930365010000017</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AB8" s="4">
+        <v>19.72023454</v>
+      </c>
+      <c r="AC8" s="44"/>
+    </row>
+    <row r="9" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
         <v>2</v>
       </c>
@@ -2446,8 +2478,12 @@
       <c r="AA9" s="28">
         <v>229.17111446000001</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB9" s="28">
+        <v>102.96332622</v>
+      </c>
+      <c r="AC9" s="44"/>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2529,8 +2565,12 @@
       <c r="AA10" s="4">
         <v>226.46469877000001</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB10" s="4">
+        <v>101.35927656999999</v>
+      </c>
+      <c r="AC10" s="44"/>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
@@ -2612,8 +2652,12 @@
       <c r="AA11" s="4">
         <v>2.70641569</v>
       </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB11" s="4">
+        <v>1.6040496500000059</v>
+      </c>
+      <c r="AC11" s="44"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
         <v>3</v>
       </c>
@@ -2695,8 +2739,12 @@
       <c r="AA12" s="28">
         <v>23.582730290000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB12" s="28">
+        <v>10.45657215</v>
+      </c>
+      <c r="AC12" s="44"/>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -2778,8 +2826,12 @@
       <c r="AA13" s="4">
         <v>7.9405131999999998</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB13" s="4">
+        <v>4.2824110099999997</v>
+      </c>
+      <c r="AC13" s="44"/>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -2861,8 +2913,12 @@
       <c r="AA14" s="4">
         <v>15.642217090000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB14" s="4">
+        <v>6.1741611400000007</v>
+      </c>
+      <c r="AC14" s="44"/>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
         <v>4</v>
       </c>
@@ -2944,8 +3000,12 @@
       <c r="AA15" s="28">
         <v>9.7338877899999989</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB15" s="28">
+        <v>4.0503288099999999</v>
+      </c>
+      <c r="AC15" s="44"/>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
@@ -3027,8 +3087,12 @@
       <c r="AA16" s="4">
         <v>0.57268735999999998</v>
       </c>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB16" s="4">
+        <v>0.20977499999999999</v>
+      </c>
+      <c r="AC16" s="44"/>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
@@ -3110,8 +3174,12 @@
       <c r="AA17" s="4">
         <v>9.1612004299999992</v>
       </c>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB17" s="4">
+        <v>3.8405538099999998</v>
+      </c>
+      <c r="AC17" s="44"/>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
         <v>5</v>
       </c>
@@ -3193,67 +3261,71 @@
       <c r="AA18" s="28">
         <v>0.21086457</v>
       </c>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB18" s="28">
+        <v>2.4285500000000002E-2</v>
+      </c>
+      <c r="AC18" s="44"/>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T19" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U19" s="34">
         <v>0.15837269999968839</v>
@@ -3268,7 +3340,7 @@
         <v>0.15436032999999999</v>
       </c>
       <c r="Y19" s="34">
-        <v>0.16909507000000001</v>
+        <v>0.16909487000000001</v>
       </c>
       <c r="Z19" s="34">
         <v>0.18569110999999999</v>
@@ -3276,10 +3348,14 @@
       <c r="AA19" s="34">
         <v>0.21881286999999999</v>
       </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB19" s="34">
+        <v>0.12430722</v>
+      </c>
+      <c r="AC19" s="44"/>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20" s="28"/>
       <c r="C20" s="28"/>
@@ -3308,7 +3384,7 @@
       <c r="Z20" s="4"/>
       <c r="AA20" s="4"/>
     </row>
-    <row r="21" spans="1:27" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>42</v>
       </c>
@@ -3334,9 +3410,9 @@
       <c r="Z21" s="39"/>
       <c r="AA21" s="39"/>
     </row>
-    <row r="22" spans="1:27" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -3360,9 +3436,9 @@
       <c r="Z22" s="40"/>
       <c r="AA22" s="40"/>
     </row>
-    <row r="23" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -3382,7 +3458,7 @@
       <c r="W23" s="29"/>
       <c r="X23" s="29"/>
     </row>
-    <row r="24" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>41</v>
       </c>
@@ -3404,9 +3480,9 @@
       <c r="W24" s="30"/>
       <c r="X24" s="30"/>
     </row>
-    <row r="25" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25" s="41"/>
       <c r="C25" s="41"/>
@@ -3432,27 +3508,27 @@
       <c r="W25" s="30"/>
       <c r="X25" s="30"/>
     </row>
-    <row r="26" spans="1:27" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="45"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="45"/>
-      <c r="P26" s="45"/>
-    </row>
-    <row r="27" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="46"/>
+    </row>
+    <row r="27" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
       <c r="B27" s="35"/>
       <c r="C27" s="35"/>
@@ -3481,8 +3557,8 @@
       <c r="Z27" s="35"/>
       <c r="AA27" s="35"/>
     </row>
-    <row r="28" spans="1:27" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="37"/>
       <c r="C29" s="36"/>
       <c r="D29" s="36"/>
@@ -3510,8 +3586,8 @@
       <c r="Z29" s="36"/>
       <c r="AA29" s="36"/>
     </row>
-    <row r="30" spans="1:27" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="38"/>
       <c r="C31" s="38"/>
       <c r="D31" s="38"/>
@@ -3550,21 +3626,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="36.5546875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="36.5703125" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="41.109375" customWidth="1"/>
-    <col min="2" max="2" width="75.33203125" customWidth="1"/>
+    <col min="1" max="1" width="41.140625" customWidth="1"/>
+    <col min="2" max="2" width="75.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="47"/>
-    </row>
-    <row r="2" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="48"/>
+    </row>
+    <row r="2" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>16</v>
       </c>
@@ -3572,7 +3648,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>17</v>
       </c>
@@ -3580,7 +3656,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>19</v>
       </c>
@@ -3588,7 +3664,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>21</v>
       </c>
@@ -3596,15 +3672,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>23</v>
       </c>
@@ -3612,7 +3688,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>35</v>
       </c>
@@ -3620,15 +3696,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>25</v>
       </c>
@@ -3636,7 +3712,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>38</v>
       </c>
@@ -3644,7 +3720,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>27</v>
       </c>
@@ -3652,7 +3728,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>29</v>
       </c>
@@ -3660,7 +3736,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>30</v>
       </c>
@@ -3668,12 +3744,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
